--- a/projects/QNL/QNL_consistency-findings.xlsx
+++ b/projects/QNL/QNL_consistency-findings.xlsx
@@ -1157,7 +1157,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHILLED_WATER_LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>para:Chilled_Water_Loop_Network: only one instance (entity:CHW-Loop), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/projects/QNL/QNL_consistency-findings.xlsx
+++ b/projects/QNL/QNL_consistency-findings.xlsx
@@ -1157,7 +1157,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>para:Chilled_Water_Loop_Network: only one instance (entity:CHW-Loop), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHWS-MAIN-LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/projects/QNL/QNL_consistency-findings.xlsx
+++ b/projects/QNL/QNL_consistency-findings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,7 +1157,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHWS-MAIN-LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>brick:Heating_Ventilation_Air_Conditioning_System: only one instance (entity:HVAC), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rec:BasementLevel: only one instance (entity:QNL_B), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHWS-MAIN-LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rec:Building: only one instance (entity:QNL), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>rec:BasementLevel: only one instance (entity:QNL_B), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1220,13 +1220,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I-CON-8</t>
+          <t>I-CON-15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>brick:Variable_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+          <t>rec:Building: only one instance (entity:QNL), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>brick:Fan_Coil_Unit: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+          <t>brick:Variable_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1272,10 +1272,33 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
+          <t>brick:Fan_Coil_Unit: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>QNL_Ontology.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>I-CON-8</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>brick:Constant_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>QNL_Ontology.xlsx</t>
         </is>

--- a/projects/QNL/QNL_consistency-findings.xlsx
+++ b/projects/QNL/QNL_consistency-findings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,7 +1157,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>brick:Heating_Ventilation_Air_Conditioning_System: only one instance (entity:HVAC), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>brick:Chilled_Water_System: only one instance (entity:CHW-System), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHWS-MAIN-LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>brick:Heating_Ventilation_Air_Conditioning_System: only one instance (entity:HVAC), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rec:BasementLevel: only one instance (entity:QNL_B), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>para:Chilled_Water_Loop_Network: only one instance (entity:QNL_CHWS-MAIN-LOOP), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rec:Building: only one instance (entity:QNL), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>rec:BasementLevel: only one instance (entity:QNL_B), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1243,13 +1243,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I-CON-8</t>
+          <t>I-CON-15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>brick:Variable_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+          <t>rec:Building: only one instance (entity:QNL), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1272,7 +1272,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>brick:Fan_Coil_Unit: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+          <t>brick:Variable_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1295,10 +1295,33 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
+          <t>brick:Fan_Coil_Unit: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>QNL_Ontology.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>I-CON-8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>brick:Constant_Air_Volume_Box: every unit's rec:feeds target equals its rec:locatedIn target - confirm the source column means both</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>QNL_Ontology.xlsx</t>
         </is>

--- a/projects/QNL/QNL_consistency-findings.xlsx
+++ b/projects/QNL/QNL_consistency-findings.xlsx
@@ -1180,7 +1180,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>brick:Heating_Ventilation_Air_Conditioning_System: only one instance (entity:HVAC), so no cross-unit comparison is possible - integrity checks still applied</t>
+          <t>brick:HVAC_System: only one instance (entity:HVAC), so no cross-unit comparison is possible - integrity checks still applied</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
